--- a/OCT_2026/Reports/invoice pattran.xlsx
+++ b/OCT_2026/Reports/invoice pattran.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA1F35B-5497-4C69-B16A-44E044F9EDF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C4F818-F32C-40A4-A877-74CAB72F8B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="139">
   <si>
     <t>Sr.No</t>
   </si>
@@ -166,15 +166,9 @@
     <t>Serviced</t>
   </si>
   <si>
-    <t>Order at Original Location :</t>
-  </si>
-  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>Reference Invoice :</t>
-  </si>
-  <si>
     <t>CTN</t>
   </si>
   <si>
@@ -389,12 +383,6 @@
   </si>
   <si>
     <t>Meat Masala (ECO)</t>
-  </si>
-  <si>
-    <t>NTN Status:</t>
-  </si>
-  <si>
-    <t>STRN Status:</t>
   </si>
   <si>
     <t>Customer Code :</t>
@@ -1458,7 +1446,7 @@
     <xf numFmtId="43" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="347">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1993,9 +1981,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="27" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2014,15 +1999,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2121,9 +2097,6 @@
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2319,155 +2292,155 @@
     <xf numFmtId="43" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2562,15 +2535,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>640080</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>256960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2593,8 +2566,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="243840"/>
-          <a:ext cx="10431780" cy="2202180"/>
+          <a:off x="12700" y="0"/>
+          <a:ext cx="10629900" cy="2212760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2913,28 +2886,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="282" t="s">
+      <c r="A2" s="277" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="282"/>
-      <c r="C2" s="282"/>
-      <c r="D2" s="282"/>
-      <c r="E2" s="282"/>
-      <c r="F2" s="282"/>
-      <c r="G2" s="282"/>
-      <c r="H2" s="282"/>
+      <c r="B2" s="277"/>
+      <c r="C2" s="277"/>
+      <c r="D2" s="277"/>
+      <c r="E2" s="277"/>
+      <c r="F2" s="277"/>
+      <c r="G2" s="277"/>
+      <c r="H2" s="277"/>
     </row>
     <row r="3" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="283" t="s">
+      <c r="A3" s="278" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="283"/>
-      <c r="C3" s="283"/>
-      <c r="D3" s="283"/>
-      <c r="E3" s="283"/>
-      <c r="F3" s="283"/>
-      <c r="G3" s="283"/>
-      <c r="H3" s="283"/>
+      <c r="B3" s="278"/>
+      <c r="C3" s="278"/>
+      <c r="D3" s="278"/>
+      <c r="E3" s="278"/>
+      <c r="F3" s="278"/>
+      <c r="G3" s="278"/>
+      <c r="H3" s="278"/>
       <c r="J3" s="2">
         <v>1.1000000000000001</v>
       </c>
@@ -2950,10 +2923,10 @@
       <c r="N3" s="53">
         <v>0.12</v>
       </c>
-      <c r="O3" s="278" t="s">
+      <c r="O3" s="273" t="s">
         <v>37</v>
       </c>
-      <c r="P3" s="279"/>
+      <c r="P3" s="274"/>
       <c r="S3" s="53">
         <v>0.06</v>
       </c>
@@ -2969,10 +2942,10 @@
       <c r="B4" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="284" t="s">
+      <c r="C4" s="279" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="285"/>
+      <c r="D4" s="280"/>
       <c r="E4" s="66" t="s">
         <v>23</v>
       </c>
@@ -3004,7 +2977,7 @@
         <v>41</v>
       </c>
       <c r="P4" s="65" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="15.5" x14ac:dyDescent="0.3">
@@ -3467,10 +3440,10 @@
       <c r="F13" s="38">
         <v>45</v>
       </c>
-      <c r="G13" s="280" t="s">
+      <c r="G13" s="275" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="281"/>
+      <c r="H13" s="276"/>
       <c r="J13" s="47">
         <f t="shared" si="1"/>
         <v>18.18181818181818</v>
@@ -4116,10 +4089,10 @@
       <c r="F26" s="37">
         <v>30</v>
       </c>
-      <c r="G26" s="280" t="s">
+      <c r="G26" s="275" t="s">
         <v>30</v>
       </c>
-      <c r="H26" s="281"/>
+      <c r="H26" s="276"/>
       <c r="J26" s="51">
         <f t="shared" si="1"/>
         <v>27.27272727272727</v>
@@ -4651,10 +4624,10 @@
         <v>50</v>
       </c>
       <c r="F37" s="37"/>
-      <c r="G37" s="280" t="s">
+      <c r="G37" s="275" t="s">
         <v>30</v>
       </c>
-      <c r="H37" s="281"/>
+      <c r="H37" s="276"/>
       <c r="J37" s="51">
         <f t="shared" si="1"/>
         <v>45.454545454545453</v>
@@ -5343,120 +5316,120 @@
       </c>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="286"/>
-      <c r="B3" s="286"/>
-      <c r="C3" s="286"/>
-      <c r="D3" s="286"/>
-      <c r="E3" s="286"/>
-      <c r="F3" s="287"/>
-      <c r="G3" s="287"/>
-      <c r="H3" s="287"/>
-      <c r="I3" s="287"/>
-      <c r="J3" s="287"/>
-      <c r="K3" s="287"/>
-      <c r="L3" s="287"/>
-      <c r="M3" s="287"/>
-      <c r="N3" s="287"/>
-      <c r="O3" s="287"/>
-      <c r="P3" s="287"/>
-      <c r="Q3" s="287"/>
-      <c r="R3" s="287"/>
-      <c r="S3" s="287"/>
-      <c r="T3" s="287"/>
-      <c r="U3" s="287"/>
-      <c r="V3" s="287"/>
-      <c r="W3" s="287"/>
-      <c r="X3" s="287"/>
-      <c r="Y3" s="287"/>
+      <c r="A3" s="281"/>
+      <c r="B3" s="281"/>
+      <c r="C3" s="281"/>
+      <c r="D3" s="281"/>
+      <c r="E3" s="281"/>
+      <c r="F3" s="282"/>
+      <c r="G3" s="282"/>
+      <c r="H3" s="282"/>
+      <c r="I3" s="282"/>
+      <c r="J3" s="282"/>
+      <c r="K3" s="282"/>
+      <c r="L3" s="282"/>
+      <c r="M3" s="282"/>
+      <c r="N3" s="282"/>
+      <c r="O3" s="282"/>
+      <c r="P3" s="282"/>
+      <c r="Q3" s="282"/>
+      <c r="R3" s="282"/>
+      <c r="S3" s="282"/>
+      <c r="T3" s="282"/>
+      <c r="U3" s="282"/>
+      <c r="V3" s="282"/>
+      <c r="W3" s="282"/>
+      <c r="X3" s="282"/>
+      <c r="Y3" s="282"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A4" s="288" t="s">
+      <c r="A4" s="283" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="122" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="122"/>
+      <c r="D4" s="285" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="122" t="s">
+      <c r="E4" s="287" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="122"/>
-      <c r="D4" s="290" t="s">
+      <c r="F4" s="289" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="289"/>
+      <c r="H4" s="290" t="s">
         <v>97</v>
       </c>
-      <c r="E4" s="292" t="s">
+      <c r="I4" s="290"/>
+      <c r="J4" s="291" t="s">
         <v>98</v>
       </c>
-      <c r="F4" s="294" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="294"/>
-      <c r="H4" s="295" t="s">
+      <c r="K4" s="292"/>
+      <c r="L4" s="291" t="s">
         <v>99</v>
       </c>
-      <c r="I4" s="295"/>
-      <c r="J4" s="296" t="s">
+      <c r="M4" s="292"/>
+      <c r="N4" s="293" t="s">
         <v>100</v>
       </c>
-      <c r="K4" s="297"/>
-      <c r="L4" s="296" t="s">
+      <c r="O4" s="293"/>
+      <c r="P4" s="291" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q4" s="292"/>
+      <c r="R4" s="291" t="s">
         <v>101</v>
       </c>
-      <c r="M4" s="297"/>
-      <c r="N4" s="298" t="s">
+      <c r="S4" s="292"/>
+      <c r="T4" s="294" t="s">
         <v>102</v>
       </c>
-      <c r="O4" s="298"/>
-      <c r="P4" s="296" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q4" s="297"/>
-      <c r="R4" s="296" t="s">
+      <c r="U4" s="294"/>
+      <c r="V4" s="295" t="s">
         <v>103</v>
       </c>
-      <c r="S4" s="297"/>
-      <c r="T4" s="299" t="s">
+      <c r="W4" s="296"/>
+      <c r="X4" s="295" t="s">
         <v>104</v>
       </c>
-      <c r="U4" s="299"/>
-      <c r="V4" s="300" t="s">
+      <c r="Y4" s="296"/>
+    </row>
+    <row r="5" spans="1:25" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="284"/>
+      <c r="B5" s="124" t="s">
         <v>105</v>
       </c>
-      <c r="W4" s="301"/>
-      <c r="X4" s="300" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y4" s="301"/>
-    </row>
-    <row r="5" spans="1:25" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="289"/>
-      <c r="B5" s="124" t="s">
-        <v>107</v>
-      </c>
       <c r="C5" s="124" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" s="291"/>
-      <c r="E5" s="293"/>
+        <v>95</v>
+      </c>
+      <c r="D5" s="286"/>
+      <c r="E5" s="288"/>
       <c r="F5" s="125" t="s">
         <v>36</v>
       </c>
       <c r="G5" s="126" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H5" s="127" t="s">
+        <v>106</v>
+      </c>
+      <c r="I5" s="128" t="s">
+        <v>107</v>
+      </c>
+      <c r="J5" s="129" t="s">
+        <v>106</v>
+      </c>
+      <c r="K5" s="129" t="s">
         <v>108</v>
       </c>
-      <c r="I5" s="128" t="s">
-        <v>109</v>
-      </c>
-      <c r="J5" s="129" t="s">
+      <c r="L5" s="129" t="s">
+        <v>106</v>
+      </c>
+      <c r="M5" s="129" t="s">
         <v>108</v>
-      </c>
-      <c r="K5" s="129" t="s">
-        <v>110</v>
-      </c>
-      <c r="L5" s="129" t="s">
-        <v>108</v>
-      </c>
-      <c r="M5" s="129" t="s">
-        <v>110</v>
       </c>
       <c r="N5" s="130">
         <v>0.19</v>
@@ -5477,22 +5450,22 @@
         <v>38</v>
       </c>
       <c r="T5" s="129" t="s">
+        <v>106</v>
+      </c>
+      <c r="U5" s="129" t="s">
         <v>108</v>
       </c>
-      <c r="U5" s="129" t="s">
-        <v>110</v>
-      </c>
       <c r="V5" s="129" t="s">
+        <v>106</v>
+      </c>
+      <c r="W5" s="129" t="s">
         <v>108</v>
       </c>
-      <c r="W5" s="129" t="s">
-        <v>110</v>
-      </c>
       <c r="X5" s="129" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y5" s="129" t="s">
         <v>108</v>
-      </c>
-      <c r="Y5" s="129" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
@@ -5501,13 +5474,13 @@
       </c>
       <c r="B6" s="123"/>
       <c r="C6" s="123" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D6" s="123" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E6" s="135" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F6" s="136">
         <v>70</v>
@@ -5586,13 +5559,13 @@
       </c>
       <c r="B7" s="123"/>
       <c r="C7" s="123" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D7" s="123" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E7" s="135" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F7" s="136">
         <v>70</v>
@@ -5672,13 +5645,13 @@
       </c>
       <c r="B8" s="123"/>
       <c r="C8" s="123" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D8" s="123" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E8" s="135" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F8" s="136">
         <v>70</v>
@@ -5758,13 +5731,13 @@
       </c>
       <c r="B9" s="123"/>
       <c r="C9" s="123" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D9" s="123" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E9" s="135" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F9" s="136">
         <v>120</v>
@@ -5844,13 +5817,13 @@
       </c>
       <c r="B10" s="123"/>
       <c r="C10" s="123" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D10" s="123" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E10" s="135" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F10" s="136">
         <v>120</v>
@@ -5930,13 +5903,13 @@
       </c>
       <c r="B11" s="123"/>
       <c r="C11" s="123" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D11" s="123" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E11" s="135" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F11" s="136">
         <v>120</v>
@@ -6016,13 +5989,13 @@
       </c>
       <c r="B12" s="123"/>
       <c r="C12" s="123" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D12" s="123" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E12" s="135" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F12" s="136">
         <v>60</v>
@@ -6102,13 +6075,13 @@
       </c>
       <c r="B13" s="123"/>
       <c r="C13" s="123" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D13" s="123" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E13" s="135" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F13" s="136">
         <v>60</v>
@@ -6188,13 +6161,13 @@
       </c>
       <c r="B14" s="123"/>
       <c r="C14" s="123" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D14" s="123" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E14" s="135" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F14" s="136">
         <v>60</v>
@@ -7960,7 +7933,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:XEW42"/>
+  <dimension ref="A2:XEW40"/>
   <sheetFormatPr defaultColWidth="29.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.36328125" style="61" customWidth="1"/>
@@ -7986,632 +7959,724 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24 16376:16377" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="302" t="s">
-        <v>130</v>
-      </c>
-      <c r="B2" s="302"/>
-      <c r="C2" s="302"/>
+      <c r="A2" s="346" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="346"/>
+      <c r="C2" s="346"/>
     </row>
     <row r="3" spans="1:24 16376:16377" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="303" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="303"/>
-      <c r="C3" s="303"/>
+      <c r="A3" s="343" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="343"/>
+      <c r="C3" s="343"/>
       <c r="F3" s="81"/>
       <c r="G3" s="81"/>
       <c r="H3" s="1"/>
-      <c r="L3" s="304" t="s">
+      <c r="L3" s="341" t="s">
         <v>43</v>
       </c>
-      <c r="M3" s="304"/>
-      <c r="N3" s="304"/>
-      <c r="O3" s="303"/>
-      <c r="P3" s="303"/>
-      <c r="Q3" s="303"/>
+      <c r="M3" s="341"/>
+      <c r="N3" s="341"/>
+      <c r="O3" s="343"/>
+      <c r="P3" s="343"/>
+      <c r="Q3" s="343"/>
       <c r="S3" s="81"/>
-      <c r="T3" s="193"/>
+      <c r="T3" s="192"/>
       <c r="XEV3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="XEW3" s="112">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="4" spans="1:24 16376:16377" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="303" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="303"/>
-      <c r="C4" s="303"/>
+      <c r="A4" s="343" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="343"/>
+      <c r="C4" s="343"/>
       <c r="F4" s="81"/>
       <c r="G4" s="81"/>
       <c r="H4" s="1"/>
-      <c r="L4" s="304" t="s">
+      <c r="L4" s="341" t="s">
         <v>44</v>
       </c>
-      <c r="M4" s="304"/>
-      <c r="N4" s="304"/>
-      <c r="O4" s="305">
+      <c r="M4" s="341"/>
+      <c r="N4" s="341"/>
+      <c r="O4" s="345">
         <f ca="1">TODAY()+1</f>
         <v>46304</v>
       </c>
-      <c r="P4" s="305"/>
-      <c r="Q4" s="305"/>
-      <c r="S4" s="261"/>
-      <c r="T4" s="262"/>
-      <c r="U4" s="263"/>
-      <c r="V4" s="263"/>
-      <c r="W4" s="264"/>
-      <c r="X4" s="264"/>
+      <c r="P4" s="345"/>
+      <c r="Q4" s="345"/>
+      <c r="S4" s="256"/>
+      <c r="T4" s="257"/>
+      <c r="U4" s="258"/>
+      <c r="V4" s="258"/>
+      <c r="W4" s="259"/>
+      <c r="X4" s="259"/>
       <c r="XEV4" s="83" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="XEW4" s="112">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:24 16376:16377" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="306" t="s">
-        <v>125</v>
-      </c>
-      <c r="B5" s="306"/>
-      <c r="C5" s="306"/>
+      <c r="A5" s="344" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="344"/>
+      <c r="C5" s="344"/>
       <c r="F5" s="81"/>
       <c r="G5" s="81"/>
       <c r="H5" s="1"/>
-      <c r="L5" s="304" t="s">
+      <c r="L5" s="341" t="s">
         <v>45</v>
       </c>
-      <c r="M5" s="304"/>
-      <c r="N5" s="304"/>
-      <c r="O5" s="305">
+      <c r="M5" s="341"/>
+      <c r="N5" s="341"/>
+      <c r="O5" s="345">
         <f ca="1">O4-1</f>
         <v>46303</v>
       </c>
-      <c r="P5" s="303"/>
-      <c r="Q5" s="303"/>
-      <c r="S5" s="261"/>
-      <c r="T5" s="262"/>
-      <c r="U5" s="263"/>
-      <c r="V5" s="263"/>
-      <c r="W5" s="264"/>
-      <c r="X5" s="264"/>
+      <c r="P5" s="343"/>
+      <c r="Q5" s="343"/>
+      <c r="S5" s="256"/>
+      <c r="T5" s="257"/>
+      <c r="U5" s="258"/>
+      <c r="V5" s="258"/>
+      <c r="W5" s="259"/>
+      <c r="X5" s="259"/>
     </row>
     <row r="6" spans="1:24 16376:16377" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="306" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="306"/>
-      <c r="C6" s="306"/>
+      <c r="A6" s="344" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="344"/>
+      <c r="C6" s="344"/>
       <c r="F6" s="81"/>
       <c r="G6" s="81"/>
       <c r="H6" s="82"/>
-      <c r="L6" s="304" t="s">
-        <v>65</v>
-      </c>
-      <c r="M6" s="304"/>
-      <c r="N6" s="304"/>
-      <c r="O6" s="307" t="s">
-        <v>58</v>
-      </c>
-      <c r="P6" s="307"/>
-      <c r="Q6" s="307"/>
-      <c r="S6" s="261"/>
-      <c r="T6" s="265"/>
-      <c r="U6" s="263"/>
-      <c r="V6" s="263"/>
-      <c r="W6" s="264"/>
-      <c r="X6" s="264"/>
+      <c r="L6" s="341" t="s">
+        <v>63</v>
+      </c>
+      <c r="M6" s="341"/>
+      <c r="N6" s="341"/>
+      <c r="O6" s="342" t="s">
+        <v>56</v>
+      </c>
+      <c r="P6" s="342"/>
+      <c r="Q6" s="342"/>
+      <c r="S6" s="256"/>
+      <c r="T6" s="260"/>
+      <c r="U6" s="258"/>
+      <c r="V6" s="258"/>
+      <c r="W6" s="259"/>
+      <c r="X6" s="259"/>
       <c r="XEV6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="XEW6" s="110">
         <v>0.18</v>
       </c>
     </row>
     <row r="7" spans="1:24 16376:16377" s="83" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="304" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="304"/>
-      <c r="C7" s="304"/>
+      <c r="A7" s="341" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="341"/>
+      <c r="C7" s="341"/>
       <c r="F7" s="81"/>
       <c r="G7" s="81"/>
       <c r="H7" s="82"/>
-      <c r="J7" s="194"/>
-      <c r="L7" s="304" t="s">
-        <v>62</v>
-      </c>
-      <c r="M7" s="304"/>
-      <c r="N7" s="304"/>
-      <c r="O7" s="307" t="s">
-        <v>66</v>
-      </c>
-      <c r="P7" s="307"/>
-      <c r="Q7" s="307"/>
-      <c r="S7" s="261"/>
-      <c r="T7" s="265"/>
-      <c r="U7" s="266"/>
-      <c r="V7" s="266"/>
-      <c r="W7" s="267"/>
-      <c r="X7" s="267"/>
+      <c r="J7" s="193"/>
+      <c r="L7" s="341" t="s">
+        <v>60</v>
+      </c>
+      <c r="M7" s="341"/>
+      <c r="N7" s="341"/>
+      <c r="O7" s="342" t="s">
+        <v>64</v>
+      </c>
+      <c r="P7" s="342"/>
+      <c r="Q7" s="342"/>
+      <c r="S7" s="256"/>
+      <c r="T7" s="260"/>
+      <c r="U7" s="261"/>
+      <c r="V7" s="261"/>
+      <c r="W7" s="262"/>
+      <c r="X7" s="262"/>
       <c r="XEV7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="XEW7" s="110">
         <v>0.22</v>
       </c>
     </row>
     <row r="8" spans="1:24 16376:16377" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="308" t="s">
-        <v>87</v>
-      </c>
-      <c r="B8" s="308"/>
-      <c r="C8" s="308"/>
+      <c r="A8" s="340" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="340"/>
+      <c r="C8" s="340"/>
       <c r="F8" s="81"/>
       <c r="G8" s="81"/>
       <c r="H8" s="82"/>
-      <c r="L8" s="304" t="s">
-        <v>63</v>
-      </c>
-      <c r="M8" s="304"/>
-      <c r="N8" s="304"/>
-      <c r="O8" s="307" t="s">
-        <v>67</v>
-      </c>
-      <c r="P8" s="307"/>
-      <c r="Q8" s="307"/>
-      <c r="S8" s="261"/>
-      <c r="T8" s="265"/>
-      <c r="U8" s="263"/>
-      <c r="V8" s="263"/>
-      <c r="W8" s="264"/>
-      <c r="X8" s="264"/>
+      <c r="L8" s="341" t="s">
+        <v>61</v>
+      </c>
+      <c r="M8" s="341"/>
+      <c r="N8" s="341"/>
+      <c r="O8" s="342" t="s">
+        <v>65</v>
+      </c>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
+      <c r="S8" s="256"/>
+      <c r="T8" s="260"/>
+      <c r="U8" s="258"/>
+      <c r="V8" s="258"/>
+      <c r="W8" s="259"/>
+      <c r="X8" s="259"/>
     </row>
     <row r="9" spans="1:24 16376:16377" x14ac:dyDescent="0.35">
-      <c r="A9" s="308" t="s">
-        <v>88</v>
-      </c>
-      <c r="B9" s="308"/>
-      <c r="C9" s="308"/>
+      <c r="A9" s="340" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="340"/>
+      <c r="C9" s="340"/>
       <c r="F9" s="81"/>
       <c r="G9" s="81"/>
       <c r="H9" s="82"/>
-      <c r="L9" s="304" t="s">
-        <v>64</v>
-      </c>
-      <c r="M9" s="304"/>
-      <c r="N9" s="304"/>
-      <c r="O9" s="307" t="s">
-        <v>90</v>
-      </c>
-      <c r="P9" s="307"/>
-      <c r="Q9" s="307"/>
-      <c r="S9" s="261"/>
-      <c r="T9" s="265"/>
-      <c r="U9" s="263"/>
-      <c r="V9" s="263"/>
-      <c r="W9" s="264"/>
-      <c r="X9" s="264"/>
+      <c r="L9" s="341" t="s">
+        <v>62</v>
+      </c>
+      <c r="M9" s="341"/>
+      <c r="N9" s="341"/>
+      <c r="O9" s="342" t="s">
+        <v>88</v>
+      </c>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
+      <c r="S9" s="256"/>
+      <c r="T9" s="260"/>
+      <c r="U9" s="258"/>
+      <c r="V9" s="258"/>
+      <c r="W9" s="259"/>
+      <c r="X9" s="259"/>
       <c r="XEW9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:24 16376:16377" x14ac:dyDescent="0.35">
-      <c r="A10" s="308" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="308"/>
-      <c r="C10" s="308"/>
+      <c r="A10" s="340" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="340"/>
+      <c r="C10" s="340"/>
       <c r="F10" s="81"/>
       <c r="G10" s="81"/>
       <c r="H10" s="1"/>
-      <c r="L10" s="304" t="s">
+      <c r="L10" s="341" t="s">
         <v>46</v>
       </c>
-      <c r="M10" s="304"/>
-      <c r="N10" s="304"/>
-      <c r="O10" s="303" t="s">
+      <c r="M10" s="341"/>
+      <c r="N10" s="341"/>
+      <c r="O10" s="343" t="s">
         <v>47</v>
       </c>
-      <c r="P10" s="303"/>
-      <c r="Q10" s="303"/>
-      <c r="S10" s="261"/>
-      <c r="T10" s="262"/>
-      <c r="U10" s="263"/>
-      <c r="V10" s="263"/>
-      <c r="W10" s="264"/>
-      <c r="X10" s="264"/>
+      <c r="P10" s="343"/>
+      <c r="Q10" s="343"/>
+      <c r="S10" s="256"/>
+      <c r="T10" s="257"/>
+      <c r="U10" s="258"/>
+      <c r="V10" s="258"/>
+      <c r="W10" s="259"/>
+      <c r="X10" s="259"/>
       <c r="XEW10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24 16376:16377" ht="20.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K11" s="80"/>
+      <c r="L11" s="90"/>
+      <c r="M11" s="190"/>
+      <c r="S11" s="259"/>
+      <c r="T11" s="321" t="s">
+        <v>125</v>
+      </c>
+      <c r="U11" s="321"/>
+      <c r="V11" s="321"/>
+      <c r="W11" s="259"/>
+      <c r="X11" s="259"/>
+      <c r="XEW11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24 16376:16377" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="322" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" s="324" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="326" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="99" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="322" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="328"/>
+      <c r="G12" s="328"/>
+      <c r="H12" s="329" t="s">
+        <v>50</v>
+      </c>
+      <c r="I12" s="330"/>
+      <c r="J12" s="322" t="s">
+        <v>69</v>
+      </c>
+      <c r="K12" s="332" t="s">
+        <v>77</v>
+      </c>
+      <c r="L12" s="334" t="s">
+        <v>39</v>
+      </c>
+      <c r="M12" s="336" t="s">
+        <v>129</v>
+      </c>
+      <c r="N12" s="338" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="11" spans="1:24 16376:16377" s="83" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="198" t="s">
-        <v>123</v>
-      </c>
-      <c r="B11" s="197" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="198" t="str">
-        <f>IF($P34&gt;2.49%,"No","Yes")</f>
-        <v>Yes</v>
-      </c>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="82"/>
-      <c r="J11" s="194"/>
-      <c r="L11" s="304" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" s="304"/>
-      <c r="N11" s="304"/>
-      <c r="O11" s="307" t="s">
-        <v>49</v>
-      </c>
-      <c r="P11" s="307"/>
-      <c r="Q11" s="307"/>
-      <c r="R11" s="199"/>
-      <c r="S11" s="261"/>
-      <c r="T11" s="265"/>
-      <c r="U11" s="266"/>
-      <c r="V11" s="266"/>
-      <c r="W11" s="267"/>
-      <c r="X11" s="267"/>
-    </row>
-    <row r="12" spans="1:24 16376:16377" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="233" t="s">
+      <c r="O12" s="331" t="s">
         <v>124</v>
       </c>
-      <c r="B12" s="190" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="80" t="str">
-        <f>IF($P32&gt;21.99%,"No","Yes")</f>
-        <v>Yes</v>
-      </c>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
-      <c r="H12" s="1"/>
-      <c r="L12" s="304" t="s">
-        <v>50</v>
-      </c>
-      <c r="M12" s="304"/>
-      <c r="N12" s="304"/>
-      <c r="O12" s="303"/>
-      <c r="P12" s="303"/>
-      <c r="Q12" s="303"/>
-      <c r="S12" s="261"/>
-      <c r="T12" s="262"/>
-      <c r="U12" s="263"/>
-      <c r="V12" s="263"/>
-      <c r="W12" s="264"/>
-      <c r="X12" s="264"/>
+      <c r="P12" s="91" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q12" s="84" t="s">
+        <v>51</v>
+      </c>
+      <c r="S12" s="259"/>
+      <c r="T12" s="258"/>
+      <c r="U12" s="258"/>
+      <c r="V12" s="258"/>
+      <c r="W12" s="259"/>
+      <c r="X12" s="259"/>
       <c r="XEW12" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:24 16376:16377" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="K13" s="80"/>
-      <c r="L13" s="90"/>
-      <c r="M13" s="191"/>
-      <c r="S13" s="264"/>
-      <c r="T13" s="309" t="s">
-        <v>129</v>
-      </c>
-      <c r="U13" s="309"/>
-      <c r="V13" s="309"/>
-      <c r="W13" s="264"/>
-      <c r="X13" s="264"/>
+    <row r="13" spans="1:24 16376:16377" ht="30.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="323"/>
+      <c r="B13" s="325"/>
+      <c r="C13" s="327"/>
+      <c r="D13" s="98" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="211" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13" s="218" t="s">
+        <v>127</v>
+      </c>
+      <c r="G13" s="212" t="s">
+        <v>128</v>
+      </c>
+      <c r="H13" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="119" t="s">
+        <v>41</v>
+      </c>
+      <c r="J13" s="323"/>
+      <c r="K13" s="333"/>
+      <c r="L13" s="335"/>
+      <c r="M13" s="337"/>
+      <c r="N13" s="339"/>
+      <c r="O13" s="325"/>
+      <c r="P13" s="185" t="e">
+        <f>IF(#REF!="Filer",0.5%,2.5%)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q13" s="85" t="s">
+        <v>38</v>
+      </c>
+      <c r="S13" s="259"/>
+      <c r="T13" s="263" t="s">
+        <v>54</v>
+      </c>
+      <c r="U13" s="263" t="s">
+        <v>39</v>
+      </c>
+      <c r="V13" s="263" t="s">
+        <v>122</v>
+      </c>
+      <c r="W13" s="259"/>
+      <c r="X13" s="263"/>
       <c r="XEW13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24 16376:16377" x14ac:dyDescent="0.35">
+      <c r="A14" s="229" t="s">
+        <v>136</v>
+      </c>
+      <c r="B14" s="95" t="str">
+        <f>VLOOKUP($A14,'Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <v xml:space="preserve">Meat Masala </v>
+      </c>
+      <c r="C14" s="92">
+        <f>VLOOKUP(A14,'Cust. Price List'!D6:M14,3,0)</f>
+        <v>70</v>
+      </c>
+      <c r="D14" s="196">
+        <f>VLOOKUP(A14,'Cust. Price List'!D6:M14,4,0)</f>
+        <v>40</v>
+      </c>
+      <c r="E14" s="201">
+        <f>VLOOKUP(A14,'Cust. Price List'!D6:M14,6,0)</f>
+        <v>65</v>
+      </c>
+      <c r="F14" s="247">
+        <f>VLOOKUP(A14,'Cust. Price List'!D6:M14,10,0)</f>
+        <v>52.462499999999999</v>
+      </c>
+      <c r="G14" s="202">
+        <f>+E14/1.18</f>
+        <v>55.084745762711869</v>
+      </c>
+      <c r="H14" s="248"/>
+      <c r="I14" s="249"/>
+      <c r="J14" s="250">
+        <f>(H14*D14)*F14+I14*F14</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="251">
+        <f>$J14*T14</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="252">
+        <f>$J14*U14</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="253">
+        <f>$J14*V14</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="254">
+        <f>J14-SUM(K14:M14)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="254">
+        <f>(H14*D14+I14)*(E14-E14/1.18)</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="255" t="e">
+        <f>(O14+N14)*$P$13</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q14" s="253" t="e">
+        <f>N14+O14+P14</f>
+        <v>#REF!</v>
+      </c>
+      <c r="R14" s="118"/>
+      <c r="S14" s="264"/>
+      <c r="T14" s="265">
+        <v>0.08</v>
+      </c>
+      <c r="U14" s="266">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="V14" s="265"/>
+      <c r="W14" s="259"/>
+      <c r="X14" s="264">
+        <f>D14*E14</f>
+        <v>2600</v>
+      </c>
+      <c r="XEW14" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:24 16376:16377" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="310" t="s">
-        <v>136</v>
-      </c>
-      <c r="B14" s="312" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="314" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" s="99" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="310" t="s">
-        <v>55</v>
-      </c>
-      <c r="F14" s="316"/>
-      <c r="G14" s="316"/>
-      <c r="H14" s="317" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="318"/>
-      <c r="J14" s="310" t="s">
-        <v>71</v>
-      </c>
-      <c r="K14" s="320" t="s">
-        <v>79</v>
-      </c>
-      <c r="L14" s="322" t="s">
-        <v>39</v>
-      </c>
-      <c r="M14" s="324" t="s">
+    <row r="15" spans="1:24 16376:16377" x14ac:dyDescent="0.35">
+      <c r="A15" s="230" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" s="96" t="str">
+        <f>VLOOKUP($A15,'Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <v>Lemon Tarka</v>
+      </c>
+      <c r="C15" s="93">
+        <f>VLOOKUP(B15,'Cust. Price List'!E7:P15,2,0)</f>
+        <v>70</v>
+      </c>
+      <c r="D15" s="197">
+        <f>VLOOKUP(A15,'Cust. Price List'!D7:M15,4,0)</f>
+        <v>40</v>
+      </c>
+      <c r="E15" s="203">
+        <f>VLOOKUP(A15,'Cust. Price List'!D7:M15,6,0)</f>
+        <v>65</v>
+      </c>
+      <c r="F15" s="216">
+        <f>VLOOKUP(A15,'Cust. Price List'!D7:M15,10,0)</f>
+        <v>52.462499999999999</v>
+      </c>
+      <c r="G15" s="204">
+        <f t="shared" ref="G15:G20" si="0">+E15/1.18</f>
+        <v>55.084745762711869</v>
+      </c>
+      <c r="H15" s="199"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="232">
+        <f t="shared" ref="J15:J21" si="1">(H15*D15)*F15+I15*F15</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="243">
+        <f t="shared" ref="K15:M22" si="2">$J15*T15</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="108">
+        <f>$J15*U15</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="100">
+        <f>$J15*V15</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="194">
+        <f t="shared" ref="N15:N22" si="3">J15-SUM(K15:M15)</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="194">
+        <f t="shared" ref="O15:O22" si="4">(H15*D15+I15)*(E15-E15/1.18)</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="188" t="e">
+        <f t="shared" ref="P15:P22" si="5">(O15+N15)*$P$13</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q15" s="100" t="e">
+        <f t="shared" ref="Q15:Q22" si="6">N15+O15+P15</f>
+        <v>#REF!</v>
+      </c>
+      <c r="R15" s="118"/>
+      <c r="S15" s="264"/>
+      <c r="T15" s="265">
+        <f>+T14</f>
+        <v>0.08</v>
+      </c>
+      <c r="U15" s="266">
+        <f>+U14</f>
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="V15" s="265"/>
+      <c r="W15" s="259"/>
+      <c r="X15" s="264">
+        <f t="shared" ref="X15:X20" si="7">D15*E15</f>
+        <v>2600</v>
+      </c>
+      <c r="XEW15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24 16376:16377" x14ac:dyDescent="0.35">
+      <c r="A16" s="230" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16" s="96" t="str">
+        <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <v>Chicken Chatkhara</v>
+      </c>
+      <c r="C16" s="93">
+        <f>VLOOKUP(B16,'Cust. Price List'!E8:P16,2,0)</f>
+        <v>70</v>
+      </c>
+      <c r="D16" s="197">
+        <f>VLOOKUP(A16,'Cust. Price List'!D8:M16,4,0)</f>
+        <v>40</v>
+      </c>
+      <c r="E16" s="203">
+        <f>VLOOKUP(A16,'Cust. Price List'!D8:M16,6,0)</f>
+        <v>65</v>
+      </c>
+      <c r="F16" s="216">
+        <f>VLOOKUP(A16,'Cust. Price List'!D8:M16,10,0)</f>
+        <v>52.462499999999999</v>
+      </c>
+      <c r="G16" s="204">
+        <f t="shared" si="0"/>
+        <v>55.084745762711869</v>
+      </c>
+      <c r="H16" s="199"/>
+      <c r="I16" s="88"/>
+      <c r="J16" s="232">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="243">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="108">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="100">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="194">
+        <f>J16-SUM(K16:M16)</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="194">
+        <f>(H16*D16+I16)*(E16-E16/1.18)</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="188" t="e">
+        <f t="shared" si="5"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Q16" s="100" t="e">
+        <f>N16+O16+P16</f>
+        <v>#REF!</v>
+      </c>
+      <c r="R16" s="118"/>
+      <c r="S16" s="264"/>
+      <c r="T16" s="265">
+        <f t="shared" ref="T16:T22" si="8">+T15</f>
+        <v>0.08</v>
+      </c>
+      <c r="U16" s="266">
+        <f>+U15</f>
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="V16" s="265"/>
+      <c r="W16" s="259"/>
+      <c r="X16" s="264">
+        <f t="shared" si="7"/>
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A17" s="230" t="s">
         <v>133</v>
-      </c>
-      <c r="N14" s="326" t="s">
-        <v>78</v>
-      </c>
-      <c r="O14" s="319" t="s">
-        <v>128</v>
-      </c>
-      <c r="P14" s="91" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q14" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="S14" s="264"/>
-      <c r="T14" s="263"/>
-      <c r="U14" s="263"/>
-      <c r="V14" s="263"/>
-      <c r="W14" s="264"/>
-      <c r="X14" s="264"/>
-      <c r="XEW14" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24 16376:16377" ht="30.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="311"/>
-      <c r="B15" s="313"/>
-      <c r="C15" s="315"/>
-      <c r="D15" s="98" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="215" t="s">
-        <v>127</v>
-      </c>
-      <c r="F15" s="222" t="s">
-        <v>131</v>
-      </c>
-      <c r="G15" s="216" t="s">
-        <v>132</v>
-      </c>
-      <c r="H15" s="192" t="s">
-        <v>51</v>
-      </c>
-      <c r="I15" s="119" t="s">
-        <v>41</v>
-      </c>
-      <c r="J15" s="311"/>
-      <c r="K15" s="321"/>
-      <c r="L15" s="323"/>
-      <c r="M15" s="325"/>
-      <c r="N15" s="327"/>
-      <c r="O15" s="313"/>
-      <c r="P15" s="185">
-        <f>IF(B11="Filer",0.5%,2.5%)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="Q15" s="85" t="s">
-        <v>38</v>
-      </c>
-      <c r="S15" s="264"/>
-      <c r="T15" s="268" t="s">
-        <v>56</v>
-      </c>
-      <c r="U15" s="268" t="s">
-        <v>39</v>
-      </c>
-      <c r="V15" s="268" t="s">
-        <v>126</v>
-      </c>
-      <c r="W15" s="264"/>
-      <c r="X15" s="268"/>
-      <c r="XEW15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24 16376:16377" x14ac:dyDescent="0.35">
-      <c r="A16" s="234" t="s">
-        <v>140</v>
-      </c>
-      <c r="B16" s="95" t="str">
-        <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v xml:space="preserve">Meat Masala </v>
-      </c>
-      <c r="C16" s="92">
-        <f>VLOOKUP(A16,'Cust. Price List'!D6:M14,3,0)</f>
-        <v>70</v>
-      </c>
-      <c r="D16" s="200">
-        <f>VLOOKUP(A16,'Cust. Price List'!D6:M14,4,0)</f>
-        <v>40</v>
-      </c>
-      <c r="E16" s="205">
-        <f>VLOOKUP(A16,'Cust. Price List'!D6:M14,6,0)</f>
-        <v>65</v>
-      </c>
-      <c r="F16" s="252">
-        <f>VLOOKUP(A16,'Cust. Price List'!D6:M14,10,0)</f>
-        <v>52.462499999999999</v>
-      </c>
-      <c r="G16" s="206">
-        <f>+E16/1.18</f>
-        <v>55.084745762711869</v>
-      </c>
-      <c r="H16" s="253"/>
-      <c r="I16" s="254"/>
-      <c r="J16" s="255">
-        <f>(H16*D16)*F16+I16*F16</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="256">
-        <f>$J16*T16</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="257">
-        <f>$J16*U16</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="258">
-        <f>$J16*V16</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="259">
-        <f>J16-SUM(K16:M16)</f>
-        <v>0</v>
-      </c>
-      <c r="O16" s="259">
-        <f>(H16*D16+I16)*(E16-E16/1.18)</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="260">
-        <f>(O16+N16)*$P$15</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="258">
-        <f>N16+O16+P16</f>
-        <v>0</v>
-      </c>
-      <c r="R16" s="118"/>
-      <c r="S16" s="269"/>
-      <c r="T16" s="270">
-        <v>0.08</v>
-      </c>
-      <c r="U16" s="271">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="V16" s="270"/>
-      <c r="W16" s="264"/>
-      <c r="X16" s="269">
-        <f>D16*E16</f>
-        <v>2600</v>
-      </c>
-      <c r="XEW16" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24 16377:16377" x14ac:dyDescent="0.35">
-      <c r="A17" s="235" t="s">
-        <v>142</v>
       </c>
       <c r="B17" s="96" t="str">
         <f>VLOOKUP($A17,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka</v>
+        <v>Meat Masala (Jumbo)</v>
       </c>
       <c r="C17" s="93">
-        <f>VLOOKUP(B17,'Cust. Price List'!E7:P15,2,0)</f>
-        <v>70</v>
-      </c>
-      <c r="D17" s="201">
-        <f>VLOOKUP(A17,'Cust. Price List'!D7:M15,4,0)</f>
+        <f>VLOOKUP(B17,'Cust. Price List'!E9:P17,2,0)</f>
+        <v>120</v>
+      </c>
+      <c r="D17" s="197">
+        <f>VLOOKUP(A17,'Cust. Price List'!D9:M17,4,0)</f>
         <v>40</v>
       </c>
-      <c r="E17" s="207">
-        <f>VLOOKUP(A17,'Cust. Price List'!D7:M15,6,0)</f>
-        <v>65</v>
-      </c>
-      <c r="F17" s="220">
-        <f>VLOOKUP(A17,'Cust. Price List'!D7:M15,10,0)</f>
-        <v>52.462499999999999</v>
-      </c>
-      <c r="G17" s="208">
-        <f t="shared" ref="G17:G22" si="0">+E17/1.18</f>
-        <v>55.084745762711869</v>
-      </c>
-      <c r="H17" s="203"/>
-      <c r="I17" s="88"/>
-      <c r="J17" s="237">
-        <f t="shared" ref="J17:J23" si="1">(H17*D17)*F17+I17*F17</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="248">
-        <f t="shared" ref="K17:M24" si="2">$J17*T17</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="108">
+      <c r="E17" s="233">
+        <f>VLOOKUP(A17,'Cust. Price List'!D9:M17,6,0)</f>
+        <v>90</v>
+      </c>
+      <c r="F17" s="234">
+        <f>VLOOKUP(A17,'Cust. Price List'!D9:M17,10,0)</f>
+        <v>72.64</v>
+      </c>
+      <c r="G17" s="235">
+        <f t="shared" si="0"/>
+        <v>76.271186440677965</v>
+      </c>
+      <c r="H17" s="236"/>
+      <c r="I17" s="237"/>
+      <c r="J17" s="238">
+        <f>(H17*D17)*F17+I17*F17</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="244">
+        <f>$J17*T17</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="239">
         <f>$J17*U17</f>
         <v>0</v>
       </c>
-      <c r="M17" s="100">
-        <f>$J17*V17</f>
-        <v>0</v>
-      </c>
-      <c r="N17" s="195">
-        <f t="shared" ref="N17:N24" si="3">J17-SUM(K17:M17)</f>
-        <v>0</v>
-      </c>
-      <c r="O17" s="195">
-        <f t="shared" ref="O17:O24" si="4">(H17*D17+I17)*(E17-E17/1.18)</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="188">
-        <f t="shared" ref="P17:P24" si="5">(O17+N17)*$P$15</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="100">
-        <f t="shared" ref="Q17:Q24" si="6">N17+O17+P17</f>
-        <v>0</v>
+      <c r="M17" s="240">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N17" s="241">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O17" s="241">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P17" s="242" t="e">
+        <f t="shared" si="5"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Q17" s="240" t="e">
+        <f t="shared" si="6"/>
+        <v>#REF!</v>
       </c>
       <c r="R17" s="118"/>
-      <c r="S17" s="269"/>
-      <c r="T17" s="270">
-        <f>+T16</f>
+      <c r="S17" s="264"/>
+      <c r="T17" s="265">
+        <f t="shared" si="8"/>
         <v>0.08</v>
       </c>
-      <c r="U17" s="271">
-        <f>+U16</f>
+      <c r="U17" s="266">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="V17" s="270"/>
-      <c r="W17" s="264"/>
-      <c r="X17" s="269">
-        <f t="shared" ref="X17:X22" si="7">D17*E17</f>
-        <v>2600</v>
-      </c>
-      <c r="XEW17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24 16377:16377" x14ac:dyDescent="0.35">
-      <c r="A18" s="235" t="s">
-        <v>141</v>
+      <c r="V17" s="265"/>
+      <c r="W17" s="259"/>
+      <c r="X17" s="264">
+        <f>G17/1.18*D17</f>
+        <v>2585.4639471416258</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A18" s="230" t="s">
+        <v>135</v>
       </c>
       <c r="B18" s="96" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Chicken Chatkhara</v>
+        <v>Lemon Tarka (Jumbo)</v>
       </c>
       <c r="C18" s="93">
-        <f>VLOOKUP(B18,'Cust. Price List'!E8:P16,2,0)</f>
-        <v>70</v>
-      </c>
-      <c r="D18" s="201">
-        <f>VLOOKUP(A18,'Cust. Price List'!D8:M16,4,0)</f>
+        <f>VLOOKUP(B18,'Cust. Price List'!E10:P18,2,0)</f>
+        <v>120</v>
+      </c>
+      <c r="D18" s="197">
+        <f>VLOOKUP(A18,'Cust. Price List'!D10:M18,4,0)</f>
         <v>40</v>
       </c>
-      <c r="E18" s="207">
-        <f>VLOOKUP(A18,'Cust. Price List'!D8:M16,6,0)</f>
-        <v>65</v>
-      </c>
-      <c r="F18" s="220">
-        <f>VLOOKUP(A18,'Cust. Price List'!D8:M16,10,0)</f>
-        <v>52.462499999999999</v>
-      </c>
-      <c r="G18" s="208">
+      <c r="E18" s="203">
+        <f>VLOOKUP(A18,'Cust. Price List'!D10:M18,6,0)</f>
+        <v>90</v>
+      </c>
+      <c r="F18" s="216">
+        <f>VLOOKUP(A18,'Cust. Price List'!D10:M18,10,0)</f>
+        <v>72.64</v>
+      </c>
+      <c r="G18" s="204">
         <f t="shared" si="0"/>
-        <v>55.084745762711869</v>
-      </c>
-      <c r="H18" s="203"/>
+        <v>76.271186440677965</v>
+      </c>
+      <c r="H18" s="199"/>
       <c r="I18" s="88"/>
-      <c r="J18" s="237">
+      <c r="J18" s="232">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K18" s="248">
+      <c r="K18" s="243">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -8623,152 +8688,153 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N18" s="195">
-        <f>J18-SUM(K18:M18)</f>
-        <v>0</v>
-      </c>
-      <c r="O18" s="195">
-        <f>(H18*D18+I18)*(E18-E18/1.18)</f>
-        <v>0</v>
-      </c>
-      <c r="P18" s="188">
+      <c r="N18" s="194">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="194">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="188" t="e">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="100">
-        <f>N18+O18+P18</f>
-        <v>0</v>
+        <v>#REF!</v>
+      </c>
+      <c r="Q18" s="100" t="e">
+        <f t="shared" si="6"/>
+        <v>#REF!</v>
       </c>
       <c r="R18" s="118"/>
-      <c r="S18" s="269"/>
-      <c r="T18" s="270">
-        <f t="shared" ref="T18:T24" si="8">+T17</f>
+      <c r="S18" s="264"/>
+      <c r="T18" s="265">
+        <f t="shared" si="8"/>
         <v>0.08</v>
       </c>
-      <c r="U18" s="271">
+      <c r="U18" s="266">
         <f>+U17</f>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="V18" s="270"/>
+      <c r="V18" s="265"/>
       <c r="W18" s="264"/>
-      <c r="X18" s="269">
-        <f t="shared" si="7"/>
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24 16377:16377" x14ac:dyDescent="0.35">
-      <c r="A19" s="235" t="s">
-        <v>137</v>
+      <c r="X18" s="264">
+        <f>G18/1.18*D18</f>
+        <v>2585.4639471416258</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A19" s="230" t="s">
+        <v>134</v>
       </c>
       <c r="B19" s="96" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Meat Masala (Jumbo)</v>
+        <v>Chicken Chatkhara (Jumbo)</v>
       </c>
       <c r="C19" s="93">
-        <f>VLOOKUP(B19,'Cust. Price List'!E9:P17,2,0)</f>
+        <f>VLOOKUP(B19,'Cust. Price List'!E11:P19,2,0)</f>
         <v>120</v>
       </c>
-      <c r="D19" s="201">
-        <f>VLOOKUP(A19,'Cust. Price List'!D9:M17,4,0)</f>
+      <c r="D19" s="197">
+        <f>VLOOKUP(A19,'Cust. Price List'!D11:M19,4,0)</f>
         <v>40</v>
       </c>
-      <c r="E19" s="238">
-        <f>VLOOKUP(A19,'Cust. Price List'!D9:M17,6,0)</f>
+      <c r="E19" s="203">
+        <f>VLOOKUP(A19,'Cust. Price List'!D11:M19,6,0)</f>
         <v>90</v>
       </c>
-      <c r="F19" s="239">
-        <f>VLOOKUP(A19,'Cust. Price List'!D9:M17,10,0)</f>
+      <c r="F19" s="216">
+        <f>VLOOKUP(A19,'Cust. Price List'!D11:M19,10,0)</f>
         <v>72.64</v>
       </c>
-      <c r="G19" s="240">
+      <c r="G19" s="204">
         <f t="shared" si="0"/>
         <v>76.271186440677965</v>
       </c>
-      <c r="H19" s="241"/>
-      <c r="I19" s="242"/>
-      <c r="J19" s="243">
-        <f>(H19*D19)*F19+I19*F19</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="249">
-        <f>$J19*T19</f>
-        <v>0</v>
-      </c>
-      <c r="L19" s="244">
-        <f>$J19*U19</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="245">
+      <c r="H19" s="199"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="232">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="243">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N19" s="246">
+      <c r="L19" s="108">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="100">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="194">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O19" s="246">
+      <c r="O19" s="194">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P19" s="247">
+      <c r="P19" s="188" t="e">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="245">
+        <v>#REF!</v>
+      </c>
+      <c r="Q19" s="100" t="e">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>#REF!</v>
       </c>
       <c r="R19" s="118"/>
-      <c r="S19" s="269"/>
-      <c r="T19" s="270">
+      <c r="S19" s="264"/>
+      <c r="T19" s="265">
         <f t="shared" si="8"/>
         <v>0.08</v>
       </c>
-      <c r="U19" s="271">
+      <c r="U19" s="266">
+        <f>+U18</f>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="V19" s="270"/>
-      <c r="W19" s="264"/>
-      <c r="X19" s="269">
+      <c r="V19" s="265"/>
+      <c r="W19" s="259"/>
+      <c r="X19" s="264">
         <f>G19/1.18*D19</f>
         <v>2585.4639471416258</v>
       </c>
     </row>
-    <row r="20" spans="1:24 16377:16377" x14ac:dyDescent="0.35">
-      <c r="A20" s="235" t="s">
-        <v>139</v>
+    <row r="20" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="230" t="s">
+        <v>115</v>
       </c>
       <c r="B20" s="96" t="str">
         <f>VLOOKUP($A20,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (Jumbo)</v>
+        <v>Chicken Chatkhara  (ECO)</v>
       </c>
       <c r="C20" s="93">
-        <f>VLOOKUP(B20,'Cust. Price List'!E10:P18,2,0)</f>
-        <v>120</v>
-      </c>
-      <c r="D20" s="201">
-        <f>VLOOKUP(A20,'Cust. Price List'!D10:M18,4,0)</f>
+        <f>VLOOKUP(B20,'Cust. Price List'!E12:P20,2,0)</f>
+        <v>60</v>
+      </c>
+      <c r="D20" s="197">
+        <f>VLOOKUP(A20,'Cust. Price List'!D12:M20,4,0)</f>
         <v>40</v>
       </c>
-      <c r="E20" s="207">
-        <f>VLOOKUP(A20,'Cust. Price List'!D10:M18,6,0)</f>
-        <v>90</v>
-      </c>
-      <c r="F20" s="220">
-        <f>VLOOKUP(A20,'Cust. Price List'!D10:M18,10,0)</f>
-        <v>72.64</v>
-      </c>
-      <c r="G20" s="208">
+      <c r="E20" s="205">
+        <f>VLOOKUP(A20,'Cust. Price List'!D12:M20,6,0)</f>
+        <v>50</v>
+      </c>
+      <c r="F20" s="217">
+        <f>VLOOKUP(A20,'Cust. Price List'!D12:M20,10,0)</f>
+        <v>39.230000000000004</v>
+      </c>
+      <c r="G20" s="206">
         <f t="shared" si="0"/>
-        <v>76.271186440677965</v>
-      </c>
-      <c r="H20" s="203"/>
+        <v>42.372881355932208</v>
+      </c>
+      <c r="H20" s="199"/>
       <c r="I20" s="88"/>
-      <c r="J20" s="237">
+      <c r="J20" s="232">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K20" s="248">
+      <c r="K20" s="243">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -8777,77 +8843,74 @@
         <v>0</v>
       </c>
       <c r="M20" s="100">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="195">
+        <f>(H20*D20+I20)*V20</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="194">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O20" s="195">
+      <c r="O20" s="194">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P20" s="188">
+      <c r="P20" s="188" t="e">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="100">
+        <v>#REF!</v>
+      </c>
+      <c r="Q20" s="100" t="e">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>#REF!</v>
       </c>
       <c r="R20" s="118"/>
-      <c r="S20" s="269"/>
-      <c r="T20" s="270">
-        <f t="shared" si="8"/>
-        <v>0.08</v>
-      </c>
-      <c r="U20" s="271">
-        <f>+U19</f>
+      <c r="S20" s="264"/>
+      <c r="T20" s="265">
+        <v>0.05</v>
+      </c>
+      <c r="U20" s="266">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="V20" s="270"/>
-      <c r="W20" s="269"/>
-      <c r="X20" s="269">
-        <f>G20/1.18*D20</f>
-        <v>2585.4639471416258</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24 16377:16377" x14ac:dyDescent="0.35">
-      <c r="A21" s="235" t="s">
-        <v>138</v>
+      <c r="V20" s="267">
+        <v>2</v>
+      </c>
+      <c r="W20" s="259"/>
+      <c r="X20" s="264">
+        <f t="shared" si="7"/>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="230" t="s">
+        <v>117</v>
       </c>
       <c r="B21" s="96" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Chicken Chatkhara (Jumbo)</v>
+        <v>Lemon Tarka (ECO)</v>
       </c>
       <c r="C21" s="93">
-        <f>VLOOKUP(B21,'Cust. Price List'!E11:P19,2,0)</f>
-        <v>120</v>
-      </c>
-      <c r="D21" s="201">
-        <f>VLOOKUP(A21,'Cust. Price List'!D11:M19,4,0)</f>
+        <f>VLOOKUP(B21,'Cust. Price List'!E13:P21,2,0)</f>
+        <v>60</v>
+      </c>
+      <c r="D21" s="197">
+        <f>VLOOKUP(A21,'Cust. Price List'!D13:M21,4,0)</f>
         <v>40</v>
       </c>
-      <c r="E21" s="207">
-        <f>VLOOKUP(A21,'Cust. Price List'!D11:M19,6,0)</f>
-        <v>90</v>
-      </c>
-      <c r="F21" s="220">
-        <f>VLOOKUP(A21,'Cust. Price List'!D11:M19,10,0)</f>
-        <v>72.64</v>
-      </c>
-      <c r="G21" s="208">
-        <f t="shared" si="0"/>
-        <v>76.271186440677965</v>
-      </c>
-      <c r="H21" s="203"/>
+      <c r="E21" s="201">
+        <f>VLOOKUP(A21,'Cust. Price List'!D13:M21,6,0)</f>
+        <v>50</v>
+      </c>
+      <c r="F21" s="202">
+        <f>VLOOKUP(A21,'Cust. Price List'!D13:M21,10,0)</f>
+        <v>39.230000000000004</v>
+      </c>
+      <c r="G21" s="213"/>
+      <c r="H21" s="199"/>
       <c r="I21" s="88"/>
-      <c r="J21" s="237">
+      <c r="J21" s="209">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K21" s="248">
+      <c r="K21" s="207">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -8859,86 +8922,82 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N21" s="195">
+      <c r="N21" s="186">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O21" s="195">
+      <c r="O21" s="194">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P21" s="188">
+      <c r="P21" s="188" t="e">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="100">
+        <v>#REF!</v>
+      </c>
+      <c r="Q21" s="100" t="e">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R21" s="118"/>
-      <c r="S21" s="269"/>
-      <c r="T21" s="270">
+        <v>#REF!</v>
+      </c>
+      <c r="S21" s="259"/>
+      <c r="T21" s="265">
         <f t="shared" si="8"/>
-        <v>0.08</v>
-      </c>
-      <c r="U21" s="271">
+        <v>0.05</v>
+      </c>
+      <c r="U21" s="266">
         <f>+U20</f>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="V21" s="270"/>
-      <c r="W21" s="264"/>
-      <c r="X21" s="269">
-        <f>G21/1.18*D21</f>
-        <v>2585.4639471416258</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24 16377:16377" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="235" t="s">
-        <v>117</v>
-      </c>
-      <c r="B22" s="96" t="str">
+      <c r="V21" s="266">
+        <f>+V20</f>
+        <v>2</v>
+      </c>
+      <c r="W21" s="259"/>
+      <c r="X21" s="264"/>
+    </row>
+    <row r="22" spans="1:24" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="231" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22" s="97" t="str">
         <f>VLOOKUP($A22,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Chicken Chatkhara  (ECO)</v>
-      </c>
-      <c r="C22" s="93">
-        <f>VLOOKUP(B22,'Cust. Price List'!E12:P20,2,0)</f>
+        <v>Meat Masala (ECO)</v>
+      </c>
+      <c r="C22" s="94">
+        <f>VLOOKUP(B22,'Cust. Price List'!E14:P22,2,0)</f>
         <v>60</v>
       </c>
-      <c r="D22" s="201">
-        <f>VLOOKUP(A22,'Cust. Price List'!D12:M20,4,0)</f>
+      <c r="D22" s="198">
+        <f>VLOOKUP(A22,'Cust. Price List'!D14:M22,4,0)</f>
         <v>40</v>
       </c>
-      <c r="E22" s="209">
-        <f>VLOOKUP(A22,'Cust. Price List'!D12:M20,6,0)</f>
+      <c r="E22" s="205">
+        <f>VLOOKUP(A22,'Cust. Price List'!D14:M22,6,0)</f>
         <v>50</v>
       </c>
-      <c r="F22" s="221">
-        <f>VLOOKUP(A22,'Cust. Price List'!D12:M20,10,0)</f>
+      <c r="F22" s="206">
+        <f>VLOOKUP(A22,'Cust. Price List'!D14:M22,10,0)</f>
         <v>39.230000000000004</v>
       </c>
-      <c r="G22" s="210">
-        <f t="shared" si="0"/>
-        <v>42.372881355932208</v>
-      </c>
-      <c r="H22" s="203"/>
-      <c r="I22" s="88"/>
-      <c r="J22" s="237">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="248">
+      <c r="G22" s="214"/>
+      <c r="H22" s="200"/>
+      <c r="I22" s="89"/>
+      <c r="J22" s="210">
+        <f>(H22*D22)*F22+I22*F22</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="208">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L22" s="108">
+      <c r="L22" s="109">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M22" s="100">
-        <f>(H22*D22+I22)*V22</f>
-        <v>0</v>
-      </c>
-      <c r="N22" s="195">
+      <c r="M22" s="101">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="187">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8946,596 +9005,400 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P22" s="188">
+      <c r="P22" s="189" t="e">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="100">
+        <v>#REF!</v>
+      </c>
+      <c r="Q22" s="101" t="e">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R22" s="118"/>
-      <c r="S22" s="269"/>
-      <c r="T22" s="270">
-        <v>0.05</v>
-      </c>
-      <c r="U22" s="271">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="V22" s="272">
-        <v>2</v>
-      </c>
-      <c r="W22" s="264"/>
-      <c r="X22" s="269">
-        <f t="shared" si="7"/>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24 16377:16377" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="235" t="s">
-        <v>119</v>
-      </c>
-      <c r="B23" s="96" t="str">
-        <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
-      </c>
-      <c r="C23" s="93">
-        <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
-      </c>
-      <c r="D23" s="201">
-        <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
-      </c>
-      <c r="E23" s="205">
-        <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
-      </c>
-      <c r="F23" s="206">
-        <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
-      </c>
-      <c r="G23" s="217"/>
-      <c r="H23" s="203"/>
-      <c r="I23" s="88"/>
-      <c r="J23" s="213">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="211">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L23" s="108">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="100">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N23" s="186">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O23" s="195">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P23" s="188">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="100">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S23" s="264"/>
-      <c r="T23" s="270">
+        <v>#REF!</v>
+      </c>
+      <c r="S22" s="264"/>
+      <c r="T22" s="265">
         <f t="shared" si="8"/>
         <v>0.05</v>
       </c>
-      <c r="U23" s="271">
-        <f>+U22</f>
+      <c r="U22" s="266">
+        <f>+U21</f>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="V23" s="271">
-        <f>+V22</f>
+      <c r="V22" s="266">
+        <f>+V21</f>
         <v>2</v>
       </c>
-      <c r="W23" s="264"/>
-      <c r="X23" s="269"/>
-    </row>
-    <row r="24" spans="1:24 16377:16377" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="236" t="s">
-        <v>121</v>
-      </c>
-      <c r="B24" s="97" t="str">
-        <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Meat Masala (ECO)</v>
-      </c>
-      <c r="C24" s="94">
-        <f>VLOOKUP(B24,'Cust. Price List'!E14:P22,2,0)</f>
-        <v>60</v>
-      </c>
-      <c r="D24" s="202">
-        <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
+      <c r="W22" s="259"/>
+      <c r="X22" s="268"/>
+    </row>
+    <row r="23" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="303"/>
+      <c r="B23" s="304"/>
+      <c r="C23" s="304" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="209">
-        <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
-        <v>50</v>
-      </c>
-      <c r="F24" s="210">
-        <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
-      </c>
-      <c r="G24" s="218"/>
-      <c r="H24" s="204"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="214">
-        <f>(H24*D24)*F24+I24*F24</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="212">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="109">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="101">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N24" s="187">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O24" s="196">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P24" s="189">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="101">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S24" s="269"/>
-      <c r="T24" s="270">
-        <f t="shared" si="8"/>
-        <v>0.05</v>
-      </c>
-      <c r="U24" s="271">
-        <f>+U23</f>
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="V24" s="271">
-        <f>+V23</f>
-        <v>2</v>
-      </c>
-      <c r="W24" s="264"/>
-      <c r="X24" s="273"/>
-    </row>
-    <row r="25" spans="1:24 16377:16377" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="334"/>
-      <c r="B25" s="335"/>
-      <c r="C25" s="335" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="335"/>
-      <c r="E25" s="335"/>
-      <c r="F25" s="336"/>
-      <c r="G25" s="219"/>
-      <c r="H25" s="223">
-        <f t="shared" ref="H25" si="9">SUM(H16:H24)</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="224">
-        <f t="shared" ref="I25:N25" si="10">SUM(I16:I24)</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="225">
+      <c r="D23" s="304"/>
+      <c r="E23" s="304"/>
+      <c r="F23" s="305"/>
+      <c r="G23" s="215"/>
+      <c r="H23" s="219">
+        <f t="shared" ref="H23" si="9">SUM(H14:H22)</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="220">
+        <f t="shared" ref="I23:N23" si="10">SUM(I14:I22)</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="221">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="K25" s="226">
-        <f>SUM(K16:K24)</f>
-        <v>0</v>
-      </c>
-      <c r="L25" s="227">
+      <c r="K23" s="222">
+        <f>SUM(K14:K22)</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="223">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="M25" s="228">
+      <c r="M23" s="224">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="N25" s="229">
+      <c r="N23" s="225">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="O25" s="230">
-        <f>SUM(O16:O24)</f>
-        <v>0</v>
-      </c>
-      <c r="P25" s="231">
-        <f>SUM(P16:P24)</f>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="232">
-        <f>SUM(Q16:Q24)</f>
-        <v>0</v>
-      </c>
-      <c r="S25" s="274"/>
-      <c r="T25" s="263"/>
-      <c r="U25" s="263"/>
-      <c r="V25" s="263"/>
-      <c r="W25" s="264"/>
-      <c r="X25" s="264"/>
-    </row>
-    <row r="26" spans="1:24 16377:16377" x14ac:dyDescent="0.35">
-      <c r="A26" s="103"/>
-      <c r="B26" s="103"/>
-      <c r="C26" s="103"/>
-      <c r="D26" s="103"/>
-      <c r="E26" s="103"/>
-      <c r="F26" s="103"/>
-      <c r="G26" s="103"/>
-      <c r="H26" s="104"/>
-      <c r="I26" s="104"/>
-      <c r="J26" s="105"/>
-      <c r="L26" s="106"/>
-      <c r="M26" s="106"/>
-      <c r="N26" s="106"/>
-      <c r="O26" s="106"/>
-      <c r="P26" s="107"/>
-      <c r="Q26" s="106"/>
-      <c r="S26" s="275"/>
-      <c r="T26" s="263"/>
-      <c r="U26" s="263"/>
-      <c r="V26" s="263"/>
-      <c r="W26" s="264"/>
-      <c r="X26" s="264"/>
-    </row>
-    <row r="27" spans="1:24 16377:16377" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="61"/>
-      <c r="C27" s="86"/>
-      <c r="D27" s="86"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="86"/>
-      <c r="G27" s="86"/>
-      <c r="H27" s="87"/>
-      <c r="I27" s="87"/>
-      <c r="S27" s="276"/>
-      <c r="T27" s="277"/>
-      <c r="U27" s="263"/>
-      <c r="V27" s="263"/>
-      <c r="W27" s="264"/>
-      <c r="X27" s="264"/>
-    </row>
-    <row r="28" spans="1:24 16377:16377" x14ac:dyDescent="0.35">
-      <c r="B28" s="337" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" s="338"/>
-      <c r="D28" s="338"/>
-      <c r="E28" s="338"/>
-      <c r="F28" s="338"/>
-      <c r="G28" s="338"/>
-      <c r="H28" s="338"/>
-      <c r="I28" s="338"/>
-      <c r="J28" s="338"/>
-      <c r="K28" s="338"/>
-      <c r="L28" s="338"/>
-      <c r="M28" s="339"/>
-      <c r="O28" s="346" t="s">
-        <v>57</v>
-      </c>
-      <c r="P28" s="347"/>
-      <c r="Q28" s="116">
-        <f>J25</f>
-        <v>0</v>
-      </c>
-      <c r="S28" s="264"/>
-      <c r="T28" s="277"/>
-      <c r="U28" s="263"/>
-      <c r="V28" s="263"/>
-      <c r="W28" s="264"/>
-      <c r="X28" s="264"/>
-    </row>
-    <row r="29" spans="1:24 16377:16377" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340"/>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
-      <c r="G29" s="341"/>
-      <c r="H29" s="341"/>
-      <c r="I29" s="341"/>
-      <c r="J29" s="341"/>
-      <c r="K29" s="341"/>
-      <c r="L29" s="341"/>
-      <c r="M29" s="342"/>
-      <c r="O29" s="348" t="s">
-        <v>79</v>
-      </c>
-      <c r="P29" s="349"/>
-      <c r="Q29" s="117">
-        <f>+K25</f>
-        <v>0</v>
-      </c>
-      <c r="S29" s="264"/>
-      <c r="T29" s="263"/>
-      <c r="U29" s="263"/>
-      <c r="V29" s="263"/>
-      <c r="W29" s="264"/>
-      <c r="X29" s="264"/>
-    </row>
-    <row r="30" spans="1:24 16377:16377" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="340"/>
-      <c r="C30" s="341"/>
-      <c r="D30" s="341"/>
-      <c r="E30" s="341"/>
-      <c r="F30" s="341"/>
-      <c r="G30" s="341"/>
-      <c r="H30" s="341"/>
-      <c r="I30" s="341"/>
-      <c r="J30" s="341"/>
-      <c r="K30" s="341"/>
-      <c r="L30" s="341"/>
-      <c r="M30" s="342"/>
-      <c r="O30" s="348" t="s">
-        <v>80</v>
-      </c>
-      <c r="P30" s="349"/>
-      <c r="Q30" s="117">
-        <f>+L25+M25</f>
-        <v>0</v>
-      </c>
-      <c r="S30" s="264"/>
-      <c r="T30" s="263"/>
-      <c r="U30" s="263">
+      <c r="O23" s="226">
+        <f>SUM(O14:O22)</f>
+        <v>0</v>
+      </c>
+      <c r="P23" s="227" t="e">
+        <f>SUM(P14:P22)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q23" s="228" t="e">
+        <f>SUM(Q14:Q22)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="S23" s="269"/>
+      <c r="T23" s="258"/>
+      <c r="U23" s="258"/>
+      <c r="V23" s="258"/>
+      <c r="W23" s="259"/>
+      <c r="X23" s="259"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A24" s="103"/>
+      <c r="B24" s="103"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="103"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="103"/>
+      <c r="G24" s="103"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="104"/>
+      <c r="J24" s="105"/>
+      <c r="L24" s="106"/>
+      <c r="M24" s="106"/>
+      <c r="N24" s="106"/>
+      <c r="O24" s="106"/>
+      <c r="P24" s="107"/>
+      <c r="Q24" s="106"/>
+      <c r="S24" s="270"/>
+      <c r="T24" s="258"/>
+      <c r="U24" s="258"/>
+      <c r="V24" s="258"/>
+      <c r="W24" s="259"/>
+      <c r="X24" s="259"/>
+    </row>
+    <row r="25" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="61"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="87"/>
+      <c r="I25" s="87"/>
+      <c r="S25" s="271"/>
+      <c r="T25" s="272"/>
+      <c r="U25" s="258"/>
+      <c r="V25" s="258"/>
+      <c r="W25" s="259"/>
+      <c r="X25" s="259"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="B26" s="306" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="307"/>
+      <c r="D26" s="307"/>
+      <c r="E26" s="307"/>
+      <c r="F26" s="307"/>
+      <c r="G26" s="307"/>
+      <c r="H26" s="307"/>
+      <c r="I26" s="307"/>
+      <c r="J26" s="307"/>
+      <c r="K26" s="307"/>
+      <c r="L26" s="307"/>
+      <c r="M26" s="308"/>
+      <c r="O26" s="315" t="s">
+        <v>55</v>
+      </c>
+      <c r="P26" s="316"/>
+      <c r="Q26" s="116">
+        <f>J23</f>
+        <v>0</v>
+      </c>
+      <c r="S26" s="259"/>
+      <c r="T26" s="272"/>
+      <c r="U26" s="258"/>
+      <c r="V26" s="258"/>
+      <c r="W26" s="259"/>
+      <c r="X26" s="259"/>
+    </row>
+    <row r="27" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="309"/>
+      <c r="C27" s="310"/>
+      <c r="D27" s="310"/>
+      <c r="E27" s="310"/>
+      <c r="F27" s="310"/>
+      <c r="G27" s="310"/>
+      <c r="H27" s="310"/>
+      <c r="I27" s="310"/>
+      <c r="J27" s="310"/>
+      <c r="K27" s="310"/>
+      <c r="L27" s="310"/>
+      <c r="M27" s="311"/>
+      <c r="O27" s="317" t="s">
+        <v>77</v>
+      </c>
+      <c r="P27" s="318"/>
+      <c r="Q27" s="117">
+        <f>+K23</f>
+        <v>0</v>
+      </c>
+      <c r="S27" s="259"/>
+      <c r="T27" s="258"/>
+      <c r="U27" s="258"/>
+      <c r="V27" s="258"/>
+      <c r="W27" s="259"/>
+      <c r="X27" s="259"/>
+    </row>
+    <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="309"/>
+      <c r="C28" s="310"/>
+      <c r="D28" s="310"/>
+      <c r="E28" s="310"/>
+      <c r="F28" s="310"/>
+      <c r="G28" s="310"/>
+      <c r="H28" s="310"/>
+      <c r="I28" s="310"/>
+      <c r="J28" s="310"/>
+      <c r="K28" s="310"/>
+      <c r="L28" s="310"/>
+      <c r="M28" s="311"/>
+      <c r="O28" s="317" t="s">
+        <v>78</v>
+      </c>
+      <c r="P28" s="318"/>
+      <c r="Q28" s="117">
+        <f>+L23+M23</f>
+        <v>0</v>
+      </c>
+      <c r="S28" s="259"/>
+      <c r="T28" s="258"/>
+      <c r="U28" s="258">
         <f>90*40</f>
         <v>3600</v>
       </c>
-      <c r="V30" s="263"/>
-      <c r="W30" s="264"/>
-      <c r="X30" s="264"/>
-    </row>
-    <row r="31" spans="1:24 16377:16377" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="340"/>
-      <c r="C31" s="341"/>
-      <c r="D31" s="341"/>
-      <c r="E31" s="341"/>
-      <c r="F31" s="341"/>
-      <c r="G31" s="341"/>
-      <c r="H31" s="341"/>
-      <c r="I31" s="341"/>
-      <c r="J31" s="341"/>
-      <c r="K31" s="341"/>
-      <c r="L31" s="341"/>
-      <c r="M31" s="342"/>
-      <c r="N31" s="110"/>
-      <c r="O31" s="348" t="s">
-        <v>81</v>
-      </c>
-      <c r="P31" s="349"/>
-      <c r="Q31" s="117">
-        <f>Q28-Q29-Q30</f>
-        <v>0</v>
-      </c>
-      <c r="S31" s="264"/>
-      <c r="T31" s="263"/>
-      <c r="U31" s="263">
+      <c r="V28" s="258"/>
+      <c r="W28" s="259"/>
+      <c r="X28" s="259"/>
+    </row>
+    <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="309"/>
+      <c r="C29" s="310"/>
+      <c r="D29" s="310"/>
+      <c r="E29" s="310"/>
+      <c r="F29" s="310"/>
+      <c r="G29" s="310"/>
+      <c r="H29" s="310"/>
+      <c r="I29" s="310"/>
+      <c r="J29" s="310"/>
+      <c r="K29" s="310"/>
+      <c r="L29" s="310"/>
+      <c r="M29" s="311"/>
+      <c r="N29" s="110"/>
+      <c r="O29" s="317" t="s">
+        <v>79</v>
+      </c>
+      <c r="P29" s="318"/>
+      <c r="Q29" s="117">
+        <f>Q26-Q27-Q28</f>
+        <v>0</v>
+      </c>
+      <c r="S29" s="259"/>
+      <c r="T29" s="258"/>
+      <c r="U29" s="258">
         <f>40*65</f>
         <v>2600</v>
       </c>
-      <c r="V31" s="263"/>
-      <c r="W31" s="264"/>
-      <c r="X31" s="264"/>
-    </row>
-    <row r="32" spans="1:24 16377:16377" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340"/>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
-      <c r="G32" s="341"/>
-      <c r="H32" s="341"/>
-      <c r="I32" s="341"/>
-      <c r="J32" s="341"/>
-      <c r="K32" s="341"/>
-      <c r="L32" s="341"/>
-      <c r="M32" s="342"/>
-      <c r="N32" s="110"/>
-      <c r="O32" s="113" t="s">
-        <v>134</v>
-      </c>
-      <c r="P32" s="111">
+      <c r="V29" s="258"/>
+      <c r="W29" s="259"/>
+      <c r="X29" s="259"/>
+    </row>
+    <row r="30" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="309"/>
+      <c r="C30" s="310"/>
+      <c r="D30" s="310"/>
+      <c r="E30" s="310"/>
+      <c r="F30" s="310"/>
+      <c r="G30" s="310"/>
+      <c r="H30" s="310"/>
+      <c r="I30" s="310"/>
+      <c r="J30" s="310"/>
+      <c r="K30" s="310"/>
+      <c r="L30" s="310"/>
+      <c r="M30" s="311"/>
+      <c r="N30" s="110"/>
+      <c r="O30" s="113" t="s">
+        <v>130</v>
+      </c>
+      <c r="P30" s="111">
         <v>0.18</v>
       </c>
-      <c r="Q32" s="117">
-        <f>+O25</f>
-        <v>0</v>
-      </c>
-      <c r="S32" s="264"/>
-      <c r="T32" s="263"/>
-      <c r="U32" s="263"/>
-      <c r="V32" s="263"/>
-      <c r="W32" s="264"/>
-      <c r="X32" s="264"/>
-    </row>
-    <row r="33" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="340"/>
-      <c r="C33" s="341"/>
-      <c r="D33" s="341"/>
-      <c r="E33" s="341"/>
-      <c r="F33" s="341"/>
-      <c r="G33" s="341"/>
-      <c r="H33" s="341"/>
-      <c r="I33" s="341"/>
-      <c r="J33" s="341"/>
-      <c r="K33" s="341"/>
-      <c r="L33" s="341"/>
-      <c r="M33" s="342"/>
-      <c r="N33" s="110"/>
-      <c r="O33" s="350" t="s">
-        <v>70</v>
-      </c>
-      <c r="P33" s="351"/>
-      <c r="Q33" s="117">
-        <f>Q31+Q32</f>
-        <v>0</v>
-      </c>
-      <c r="S33" s="264"/>
-      <c r="T33" s="263"/>
-      <c r="U33" s="263"/>
-      <c r="V33" s="263"/>
-      <c r="W33" s="264"/>
-      <c r="X33" s="264"/>
-    </row>
-    <row r="34" spans="2:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="343"/>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
-      <c r="G34" s="344"/>
-      <c r="H34" s="344"/>
-      <c r="I34" s="344"/>
-      <c r="J34" s="344"/>
-      <c r="K34" s="344"/>
-      <c r="L34" s="344"/>
-      <c r="M34" s="345"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="115" t="s">
-        <v>77</v>
-      </c>
-      <c r="P34" s="114">
-        <f>IF(B11="Filer",0.5%,2.5%)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="Q34" s="117">
-        <f>P34*Q33</f>
-        <v>0</v>
-      </c>
-      <c r="S34" s="264"/>
-      <c r="T34" s="263"/>
-      <c r="U34" s="263">
+      <c r="Q30" s="117">
+        <f>+O23</f>
+        <v>0</v>
+      </c>
+      <c r="S30" s="259"/>
+      <c r="T30" s="258"/>
+      <c r="U30" s="258"/>
+      <c r="V30" s="258"/>
+      <c r="W30" s="259"/>
+      <c r="X30" s="259"/>
+    </row>
+    <row r="31" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="309"/>
+      <c r="C31" s="310"/>
+      <c r="D31" s="310"/>
+      <c r="E31" s="310"/>
+      <c r="F31" s="310"/>
+      <c r="G31" s="310"/>
+      <c r="H31" s="310"/>
+      <c r="I31" s="310"/>
+      <c r="J31" s="310"/>
+      <c r="K31" s="310"/>
+      <c r="L31" s="310"/>
+      <c r="M31" s="311"/>
+      <c r="N31" s="110"/>
+      <c r="O31" s="319" t="s">
+        <v>68</v>
+      </c>
+      <c r="P31" s="320"/>
+      <c r="Q31" s="117">
+        <f>Q29+Q30</f>
+        <v>0</v>
+      </c>
+      <c r="S31" s="259"/>
+      <c r="T31" s="258"/>
+      <c r="U31" s="258"/>
+      <c r="V31" s="258"/>
+      <c r="W31" s="259"/>
+      <c r="X31" s="259"/>
+    </row>
+    <row r="32" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="312"/>
+      <c r="C32" s="313"/>
+      <c r="D32" s="313"/>
+      <c r="E32" s="313"/>
+      <c r="F32" s="313"/>
+      <c r="G32" s="313"/>
+      <c r="H32" s="313"/>
+      <c r="I32" s="313"/>
+      <c r="J32" s="313"/>
+      <c r="K32" s="313"/>
+      <c r="L32" s="313"/>
+      <c r="M32" s="314"/>
+      <c r="N32" s="90"/>
+      <c r="O32" s="115" t="s">
+        <v>75</v>
+      </c>
+      <c r="P32" s="114" t="e">
+        <f>IF(#REF!="Filer",0.5%,2.5%)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q32" s="117" t="e">
+        <f>P32*Q31</f>
+        <v>#REF!</v>
+      </c>
+      <c r="S32" s="259"/>
+      <c r="T32" s="258"/>
+      <c r="U32" s="258">
         <v>142.08000000000001</v>
       </c>
-      <c r="V34" s="263"/>
-      <c r="W34" s="264"/>
-      <c r="X34" s="264"/>
-    </row>
-    <row r="35" spans="2:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="O35" s="328" t="s">
-        <v>82</v>
-      </c>
-      <c r="P35" s="329"/>
-      <c r="Q35" s="250">
-        <f>+Q33+Q34</f>
-        <v>0</v>
-      </c>
-      <c r="S35" s="264"/>
-      <c r="T35" s="263"/>
-      <c r="U35" s="277">
-        <f>U34-Q35</f>
-        <v>142.08000000000001</v>
-      </c>
-      <c r="V35" s="263"/>
-      <c r="W35" s="264"/>
-      <c r="X35" s="264"/>
-    </row>
-    <row r="36" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="102" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="330"/>
-      <c r="D36" s="330"/>
-      <c r="E36" s="330"/>
-      <c r="F36" s="330"/>
-      <c r="G36" s="330"/>
-      <c r="H36" s="330"/>
-      <c r="I36" s="330"/>
-      <c r="J36" s="331"/>
-      <c r="K36" s="332"/>
-      <c r="L36" s="333"/>
-      <c r="S36" s="264"/>
-      <c r="T36" s="263"/>
-      <c r="U36" s="263"/>
-      <c r="V36" s="263"/>
-      <c r="W36" s="264"/>
-      <c r="X36" s="264"/>
-    </row>
-    <row r="37" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="S37" s="264"/>
-      <c r="T37" s="263"/>
-      <c r="U37" s="263"/>
-      <c r="V37" s="263"/>
-      <c r="W37" s="264"/>
-      <c r="X37" s="264"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="K41" s="118"/>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="J42" s="251"/>
-      <c r="K42" s="118"/>
+      <c r="V32" s="258"/>
+      <c r="W32" s="259"/>
+      <c r="X32" s="259"/>
+    </row>
+    <row r="33" spans="2:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O33" s="297" t="s">
+        <v>80</v>
+      </c>
+      <c r="P33" s="298"/>
+      <c r="Q33" s="245" t="e">
+        <f>+Q31+Q32</f>
+        <v>#REF!</v>
+      </c>
+      <c r="S33" s="259"/>
+      <c r="T33" s="258"/>
+      <c r="U33" s="272" t="e">
+        <f>U32-Q33</f>
+        <v>#REF!</v>
+      </c>
+      <c r="V33" s="258"/>
+      <c r="W33" s="259"/>
+      <c r="X33" s="259"/>
+    </row>
+    <row r="34" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="102" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" s="299"/>
+      <c r="D34" s="299"/>
+      <c r="E34" s="299"/>
+      <c r="F34" s="299"/>
+      <c r="G34" s="299"/>
+      <c r="H34" s="299"/>
+      <c r="I34" s="299"/>
+      <c r="J34" s="300"/>
+      <c r="K34" s="301"/>
+      <c r="L34" s="302"/>
+      <c r="S34" s="259"/>
+      <c r="T34" s="258"/>
+      <c r="U34" s="258"/>
+      <c r="V34" s="258"/>
+      <c r="W34" s="259"/>
+      <c r="X34" s="259"/>
+    </row>
+    <row r="35" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S35" s="259"/>
+      <c r="T35" s="258"/>
+      <c r="U35" s="258"/>
+      <c r="V35" s="258"/>
+      <c r="W35" s="259"/>
+      <c r="X35" s="259"/>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="K39" s="118"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="J40" s="246"/>
+      <c r="K40" s="118"/>
     </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="52">
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="C36:J36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="B28:M34"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="T13:V13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="O6:Q6"/>
+  <mergeCells count="48">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="L3:N3"/>
@@ -9543,19 +9406,54 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="T11:V11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="O12:O13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="C34:J34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="B26:M32"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="O31:P31"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{6BD25F0E-E90E-48FD-8D04-E34D8B25F49F}">
-      <formula1>$XEV$3:$XEV$4</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12" xr:uid="{AB312DCD-E539-476F-B08E-29ABB0E8EED3}">
-      <formula1>$XEV$6:$XEV$7</formula1>
-    </dataValidation>
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O6:Q6" xr:uid="{FAA35258-2644-4FF7-99A8-C0897083A970}">
       <formula1>#REF!</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O9:Q9" xr:uid="{6E85FB61-FA97-4B9A-B0DC-A17FCB9113DF}">
-      <formula1>$XEW$12:$XFD$17</formula1>
+      <formula1>$XEW$11:$XFD$15</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
